--- a/tools/importer/reports/import-elektromobilitaet.report.xlsx
+++ b/tools/importer/reports/import-elektromobilitaet.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,9 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>damAssets</t>
+  </si>
+  <si>
     <t>livechatWidgetsRemoved</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
     <t>["cards-teaser","columns-media-text","cards-image-overlay"]</t>
   </si>
   <si>
+    <t>{"1920x1080_E-Vorteile_Q6_SB_2023_5285_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:766808f7-b740-4399-80bf-30c6ffcf90aa/original/as/1920x1080_E-Vorteile_Q6_SB_2023_5285_01.jpg","1920x1080_E-Fahrzeuge_A6e_2023_6017_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a5928a7f-6ff6-4cec-aa89-3ebfd56b1609/original/as/1920x1080_E-Fahrzeuge_A6e_2023_6017_01.jpg","1920x1080_A5_E_2024_7736_no_Cast-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6e40c173-687b-420c-a20f-474609741022/original/as/1920x1080_A5_E_2024_7736_no_Cast-(original).jpg","1920x1080_Laden_sq6_2023_5304-cast-36346113_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ce866967-bdef-4fa5-ad0d-6c6fde16ff41/original/as/1920x1080_Laden_sq6_2023_5304-cast-36346113_01.jpg","1920x1080_bidi_stillbild-animation.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:18e2fed5-17fb-49d8-a39d-697aa73e885b/original/as/1920x1080_bidi_stillbild-animation.jpg","1920x1080_E-Foerderung_A3_2023_5821_Cast.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d51bd1ea-e5a8-47c8-970b-16f65de1e030/original/as/1920x1080_E-Foerderung_A3_2023_5821_Cast.jpg","1920x1080_e-mob_reichweite_A6e_2023_5921_2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:66a5ab2a-8920-42e3-b8cf-d3059ad85ba5/original/as/1920x1080_e-mob_reichweite_A6e_2023_5921_2_02.jpg","1920x1080_qdiv_p_181005_rgb-12566-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d858a757-a888-4f13-b141-c05a9f9ef159/original/as/1920x1080_qdiv_p_181005_rgb-12566-(original).jpg","1920x1080_Zubehoer_A6e_as_2023_6023_roof_box_closed_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cf02c1c0-8469-4fef-a7ad-939512052326/original/as/1920x1080_Zubehoer_A6e_as_2023_6023_roof_box_closed_1_01.jpg","1920x1080_ADM_as_2025_7853.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a899808d-433d-479b-a5b4-f01935209dfd/original/as/1920x1080_ADM_as_2025_7853.jpg","1920x1920_e-mob_reichweite_A6e_2023_5921_2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e2c42a97-8d7f-4a9d-8382-56708bb3c827/original/as/1920x1920_e-mob_reichweite_A6e_2023_5921_2_02.jpg","1920x1920_Ladezeit_A6e_2023_6002_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:65cf45f4-383f-4163-ab61-d0b87a001473/original/as/1920x1920_Ladezeit_A6e_2023_6002_1_01.jpg","1920x1920_Ladekarte_Q6_SB_2023_5214_withoutcast_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e5e312d9-7fe7-4a92-a404-157135a5ae3d/original/as/1920x1920_Ladekarte_Q6_SB_2023_5214_withoutcast_1_01.jpg","1920x1080_Q4_r_2022_4070_1-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e75bb944-4c7f-4f89-98f2-6db62d0e9dd3/original/as/1920x1080_Q4_r_2022_4070_1-(original).jpg"}</t>
+  </si>
+  <si>
     <t>de/elektromobilitaet</t>
   </si>
   <si>
@@ -55,13 +61,181 @@
     <t>elektromobilitaet</t>
   </si>
   <si>
-    <t>2026-10-26T18:05:41.040Z</t>
+    <t>2026-10-27T12:51:03.082Z</t>
   </si>
   <si>
     <t>E-Mobilität im Alltag | Audi Deutschland</t>
   </si>
   <si>
     <t>https://www.audi.de/de/elektromobilitaet/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","cards-stats","carousel-cards","columns-gallery","columns-media-text","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>{"A2e_2026_9665-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:f7c4f266-7067-4585-a86f-21c9698c33ff/original/as/A2e_2026_9665-S.jpg","A2e_2026_9667-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:9dfe0a2e-b4aa-4547-9908-67fb709a4d53/original/as/A2e_2026_9667-L.jpg","A2_2027_Alpha_B_3_016_DoorHandles-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:3c8e51ea-31cf-4623-b57f-0a6397782b88/original/as/A2_2027_Alpha_B_3_016_DoorHandles-L.png","A2e_2026_9691-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:5684bdaf-77c2-41ef-a2b3-c07295356f4b/original/as/A2e_2026_9691-L.jpg","A2e_2026_9677-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1c7b7cda-ff32-41f3-b517-d9f96c0e87a4/original/as/A2e_2026_9677-L.jpg","A2e_2026_9685_2-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:89a76937-9bcc-4157-950a-be2cf2dfee1c/original/as/A2e_2026_9685_2-L.jpg","A2_2027_Alpha_C_2_047_CentreConsoleWithDualCharging-S-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:98a47897-cf94-45a0-a461-b7cf281e22ba/original/as/A2_2027_Alpha_C_2_047_CentreConsoleWithDualCharging-S-L.png","A2e_2026_9676__sensors-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:542d08d9-e769-4889-99d5-e5a8f6c39fde/original/as/A2e_2026_9676__sensors-L.jpg","A2e_2026_9668-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4dfc63e6-4358-4a30-8b4f-c3e554784791/original/as/A2e_2026_9668-L.jpg","A2_2027_Alpha_B_5_019_VehicleToLoad-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1beb008a-8e4d-4354-b85d-c4bfb8af96c7/original/as/A2_2027_Alpha_B_5_019_VehicleToLoad-L.jpg","Bild-8-7-2026-0-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:9501f9f8-84d0-40ea-ba27-7a85011e0900/original/as/Bild-8-7-2026-0-L.jpg","A2e_2026_9685-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2eb4aeae-7400-4ddf-8275-b2c00e73cda3/original/as/A2e_2026_9685-L.jpg","A2_2027_Alpha_A_1_000_ExtDesignGeneral-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:07bce207-4395-4d4f-a94a-e09122fb840d/original/as/A2_2027_Alpha_A_1_000_ExtDesignGeneral-L.png","A2e_2026_9674-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:45dba5cf-a949-457e-b239-978f66eb014b/original/as/A2e_2026_9674-L.jpg","A2e_2026_9666-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2d5f2575-113d-4a10-8d7a-03ec943ba06c/original/as/A2e_2026_9666-L.jpg","Q3eh_SB_2025_8141-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:980af30d-40d0-4227-ae9e-8c5d17643c09/original/as/Q3eh_SB_2025_8141-L.jpg","Q4_e_tron_PA_SB_AU316_Alpha_A_3_000_V6V6_Light-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2731c7f1-f7f8-451d-b3e7-d6be9c96c08c/original/as/Q4_e_tron_PA_SB_AU316_Alpha_A_3_000_V6V6_Light-L.png","Q6_SB_2023_5211_3_withoutCast-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6adc14a2-82d5-4a92-8442-6d6dc5f7a401/original/as/Q6_SB_2023_5211_3_withoutCast-S-L.jpg","A2_Headeranimation_L-new.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8bd300a5-e64a-48d8-b706-2c9c5b160555/original/as/A2_Headeranimation_L-new.mp4","Audi_A2_e-tron_Reveal_Main_Longversion_16x9_DE-L.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:bad6c591-43d8-48f1-a23f-3aff53e8ce29/original/as/Audi_A2_e-tron_Reveal_Main_Longversion_16x9_DE-L.mp4","A2_SignatureCollection_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:c5a61460-15e0-4032-b1c4-8d0744863bf9/original/as/A2_SignatureCollection_S.mp4","Alpha_C_2_050_FidlockSystemInclAccessories_Animation-S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:88e19c42-562b-4c7b-9fe6-94e8c5713f6e/original/as/Alpha_C_2_050_FidlockSystemInclAccessories_Animation-S.mp4","preisliste_a2-e-tron.pdf":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:78658b75-1325-4f7d-bc69-2df0c5e57644/original/as/preisliste_a2-e-tron.pdf"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a2-e-tron/a2-e-tron</t>
+  </si>
+  <si>
+    <t>neuwagen-model</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:02:00.661Z</t>
+  </si>
+  <si>
+    <t>A2 e-tron Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/a2-e-tron/a2-e-tron/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-allstreet.report.json</t>
+  </si>
+  <si>
+    <t>{"A3_allstreet_PA2_Alpha_A_1_000_Dark-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:f026cb8d-010e-4e80-9bee-516c2e51e806/original/as/A3_allstreet_PA2_Alpha_A_1_000_Dark-L.png","A3_allstreet_PA2_Alpha_A_2_000_Dark-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8e84eec1-e42c-496a-8e2f-f38ca7bb7975/original/as/A3_allstreet_PA2_Alpha_A_2_000_Dark-L.png","A3_Allstreet_PA2_Alpha_C_2_006-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:3a318896-9cb8-460b-865c-cfba4c2f5262/original/as/A3_Allstreet_PA2_Alpha_C_2_006-L-new.png","Q7_2023_5393_1-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:54a60912-4a53-43de-8267-74d9cd2503b2/original/as/Q7_2023_5393_1-S.png","Q3eh_2025_8078_DE-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e3fdaf0b-f64d-4712-a678-2c856a7a67f8/original/as/Q3eh_2025_8078_DE-S.png","A3_Allstreet_PA2_Alpha_C_2_003-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:b504f192-4605-42e8-8d73-092008655bcc/original/as/A3_Allstreet_PA2_Alpha_C_2_003-L-new.png","A3_all_2026_9436-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e4d8258d-eb50-4c49-9734-040eb3d134c6/original/as/A3_all_2026_9436-L.jpg","A3_allstreet_PA2_Alpha_A_1_000-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:33b4ebb3-9b6e-4a81-8af4-84ace30c51ef/original/as/A3_allstreet_PA2_Alpha_A_1_000-L.png","A3_allstreet_PA2_Alpha_A_3_000-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:f903aba2-c2e6-4ed4-ad46-687cdf2d9983/original/as/A3_allstreet_PA2_Alpha_A_3_000-L-new.png","A3_Allstreet_PA2_Alpha_C_1_000-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:60014fb6-29ab-42ee-9533-18bfc6e4d4f7/original/as/A3_Allstreet_PA2_Alpha_C_1_000-L-new.png","A3_allstreet_PA2_Alpha_A_6_000-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a4ef65be-5123-44e1-87fe-2d6a2b921caa/original/as/A3_allstreet_PA2_Alpha_A_6_000-L.png","Q3_2025_8058_Cast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e15c6a3d-7dcb-4593-a630-92d44f138936/original/as/Q3_2025_8058_Cast-L.jpg","Q4_e_tron_PA_SUV_AU316_Alpha_A_3_000_3D3D_Light-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e7f9218f-f858-4bae-9f42-7fe4d0a90446/original/as/Q4_e_tron_PA_SUV_AU316_Alpha_A_3_000_3D3D_Light-L.png","Q5_2024_6815_2_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2a88f953-4588-4f11-859e-deb07e3877da/original/as/Q5_2024_6815_2_withoutCast-L.jpg","A3_PA2_allstreet_HeaderAnimation_L.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:dbc45f0f-891c-456a-8413-973ff6f3390e/original/as/A3_PA2_allstreet_HeaderAnimation_L.mp4","A3_PA2_allstreet_SignatureCollection_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:185a9e03-deec-4949-a7e2-26ab5e04dfe1/original/as/A3_PA2_allstreet_SignatureCollection_S.mp4","A3_PA2_allstreet_SeatingBallet_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:191d5877-566e-4f43-bc1e-2daf94b4d615/original/as/A3_PA2_allstreet_SeatingBallet_S.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-allstreet</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:01:48.260Z</t>
+  </si>
+  <si>
+    <t>A3 allstreet Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/a3/a3-allstreet/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-limousine.report.json</t>
+  </si>
+  <si>
+    <t>{"A3_Limousine_PA2_Alpha_A_1_000_Dark-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1a6b351c-5813-48dc-abf0-d33159736dab/original/as/A3_Limousine_PA2_Alpha_A_1_000_Dark-S.png","A3_Limousine_PA2_Alpha_A_2_000_Dark-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ef39d2d2-1e05-461d-ba5a-18550f55f4b3/original/as/A3_Limousine_PA2_Alpha_A_2_000_Dark-L.png","A3_Limousine_PA2_Alpha_C_2_006-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:b9560ef9-3c99-4863-92f2-c2a78273d440/original/as/A3_Limousine_PA2_Alpha_C_2_006-L.png","Q7_2023_5393_1-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:54a60912-4a53-43de-8267-74d9cd2503b2/original/as/Q7_2023_5393_1-S.png","Q3eh_2025_8078_DE-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e3fdaf0b-f64d-4712-a678-2c856a7a67f8/original/as/Q3eh_2025_8078_DE-S.png","A3_Limousine_PA2_Alpha_C_2_003-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1edbc0fa-0cc9-497b-aea4-5ab953bab657/original/as/A3_Limousine_PA2_Alpha_C_2_003-L.png","A3_2026_9406-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:baec1f92-d001-4238-a774-4373de9ece5f/original/as/A3_2026_9406-L.jpg","A3_Limousine_PA2_Alpha_A_1_000-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:c52e0527-819d-4b84-8277-a7b0157a2404/original/as/A3_Limousine_PA2_Alpha_A_1_000-L.png","A3_Limousine_PA2_Alpha_C_2_001-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:74fc179b-be4f-4e28-a121-b3b6dc308a84/original/as/A3_Limousine_PA2_Alpha_C_2_001-L.png","A3_Limousine_PA2_Alpha_C_2_014-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6aa9ffb7-2e0b-4a6f-9698-5443b2227c3d/original/as/A3_Limousine_PA2_Alpha_C_2_014-L.png","A3_Limousine_PA2_Alpha_A_6_000-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ec3b6e4d-8f3d-491e-a351-83799b01e027/original/as/A3_Limousine_PA2_Alpha_A_6_000-L.png","A5_2023_6207-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:69257d68-2f05-40d3-84a6-65352584186a/original/as/A5_2023_6207-L.jpg","A6_2024_7589_1-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:84b70a8c-6a74-4687-ab97-7a5d0f86c416/original/as/A6_2024_7589_1-S.jpg","Q5_2024_7162_V2-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2fcb6204-16ac-4536-b54c-1afdbe16622b/original/as/Q5_2024_7162_V2-S-L.jpg","A3_PA2_Limousine_HeaderAnimation_L.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4ff9f68b-eab8-43b5-b6a0-3a29ca9de1b1/original/as/A3_PA2_Limousine_HeaderAnimation_L.mp4","A3_PA2_Limousine_SignatureCollection_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:fc3bdd56-779b-45ba-b084-a51421dc8d74/original/as/A3_PA2_Limousine_SignatureCollection_S.mp4","A3_PA2_Limousine_SeatingBallet_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8d0c216b-09cc-4f9f-b0df-64c74b6b9fdf/original/as/A3_PA2_Limousine_SeatingBallet_S.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-limousine</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:01:43.472Z</t>
+  </si>
+  <si>
+    <t>A3 Limousine Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/a3/a3-limousine/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-sportback-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>{"A3_Sportback_TFSIe_PA2_Alpha_A_1_000_Dark-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8e916e8b-5037-453a-9c8a-7ea88648d926/original/as/A3_Sportback_TFSIe_PA2_Alpha_A_1_000_Dark-S.png","A3_Sportback_TFSIe_PA2_Alpha_A_4_000_Dark-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:72520718-33bd-49c4-be50-af504655094c/original/as/A3_Sportback_TFSIe_PA2_Alpha_A_4_000_Dark-L.png","A3_Sportback_TFSIe_PA2_Alpha_A_2_001-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:7f879602-4435-4ce1-a61c-935e949fb4dc/original/as/A3_Sportback_TFSIe_PA2_Alpha_A_2_001-L-new.png","A3_Sportback_TFSIe_PA2_Alpha_C_2_006-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:10ef2a16-8696-465b-9c2c-8b501076ad1d/original/as/A3_Sportback_TFSIe_PA2_Alpha_C_2_006-L.png","Q7_2023_5393_1-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:54a60912-4a53-43de-8267-74d9cd2503b2/original/as/Q7_2023_5393_1-S.png","Q3eh_2025_8078_DE-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e3fdaf0b-f64d-4712-a678-2c856a7a67f8/original/as/Q3eh_2025_8078_DE-S.png","A3_Sportback_TFSIe_PA2_Alpha_C_2_003-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:91300a8f-3aa3-48b9-8189-060eccbcced2/original/as/A3_Sportback_TFSIe_PA2_Alpha_C_2_003-L.png","A3_Sportback_TFSIe_PA2_Alpha_A_1_000-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8eb9836d-b283-45e0-a0e1-0a553b0ad365/original/as/A3_Sportback_TFSIe_PA2_Alpha_A_1_000-L.png","A3_Sportback_TFSIe_PA2_Alpha_C_2_007-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:de34b04c-668c-439b-a924-9d0d2c3f244d/original/as/A3_Sportback_TFSIe_PA2_Alpha_C_2_007-L.png","A3_sb_2026_9379-L-new.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:9aa8a66e-98bc-4be3-b8ed-a79eee5354ef/original/as/A3_sb_2026_9379-L-new.jpg","A3_Sportback_TFSIe_PA2_Alpha_A_4_001-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d47175ed-0e8c-4534-bf46-b85433b384e0/original/as/A3_Sportback_TFSIe_PA2_Alpha_A_4_001-L-new.png","A3_Sportback_TFSIe_PA2_Alpha_A_6_000-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:558e2a93-9bd4-4ea6-80ff-0d3e294fc9e5/original/as/A3_Sportback_TFSIe_PA2_Alpha_A_6_000-L.png","A5_E_2024_7741_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:af9228bb-1d44-4af0-8337-99d91b198c8a/original/as/A5_E_2024_7741_1-L.jpg","A6eh_2024_7668_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:eeeb5cd4-30d4-49b6-af55-bcb1051fb04e/original/as/A6eh_2024_7668_1-L.jpg","Q5_2024_6865_1_withoutCast-L-2.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:75397c66-00ab-4e55-8557-e3ea08f189ea/original/as/Q5_2024_6865_1_withoutCast-L-2.jpg","A3_PA2_Sportback_TFSIe_HeaderAnimation_L.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:23cefb6c-d666-44d7-82b5-00739ea65127/original/as/A3_PA2_Sportback_TFSIe_HeaderAnimation_L.mp4","A3_PA2_Sportback_TFSIe_SignatureCollection_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a30aa55e-1026-4b6b-8707-a8ef2b65a3d6/original/as/A3_PA2_Sportback_TFSIe_SignatureCollection_S.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-sportback-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:01:51.540Z</t>
+  </si>
+  <si>
+    <t>A3 Sportback e-hybrid Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/a3/a3-sportback-e-hybrid/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-sportback.report.json</t>
+  </si>
+  <si>
+    <t>{"A3_Sportback_PA2_Alpha_A_1_000_Dark-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:43b30600-11c2-46d6-83a2-054aabc81c7c/original/as/A3_Sportback_PA2_Alpha_A_1_000_Dark-S.png","A3_Sportback_PA2_Alpha_A_2_000_Dark-L-new-2.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:7613b004-a7f7-42e9-bbca-7eae988ec130/original/as/A3_Sportback_PA2_Alpha_A_2_000_Dark-L-new-2.png","A3_Sportback_PA2_Alpha_C_2_006-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1c9ff97c-d6d3-44ac-b6ec-1f977d65a1e8/original/as/A3_Sportback_PA2_Alpha_C_2_006-L.png","Q7_2023_5393_1-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:54a60912-4a53-43de-8267-74d9cd2503b2/original/as/Q7_2023_5393_1-S.png","Q3eh_2025_8078_DE-S.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e3fdaf0b-f64d-4712-a678-2c856a7a67f8/original/as/Q3eh_2025_8078_DE-S.png","A3_Sportback_PA2_Alpha_C_2_003-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6ac50b08-9773-43f7-a485-e03a706f08b6/original/as/A3_Sportback_PA2_Alpha_C_2_003-L.png","A3_sb_2026_9348-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:52e3e70b-360a-4fc3-bd9d-e4e7ccfb3b68/original/as/A3_sb_2026_9348-L.jpg","A3_Sportback_PA2_Alpha_A_1_000-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d864dce9-7dcd-4103-98a7-04d9c43dfcef/original/as/A3_Sportback_PA2_Alpha_A_1_000-L-new.png","A3_Sportback_PA2_Alpha_C_2_001-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cd36677c-2f8a-4049-b5ed-18b63346a865/original/as/A3_Sportback_PA2_Alpha_C_2_001-L.png","A3_Sportback_PA2_Alpha_C_2_014-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:78d1fb82-c6a1-4706-8da7-64b4e68c9a99/original/as/A3_Sportback_PA2_Alpha_C_2_014-L.png","A3_Sportback_PA2_Alpha_A_6_000-L-new.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:20058eff-4c39-4cc7-ae4a-e84c304a9bf4/original/as/A3_Sportback_PA2_Alpha_A_6_000-L-new.png","A5_2023_6318_2-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d01a193d-c4b8-493c-9360-a32da58f8ac8/original/as/A5_2023_6318_2-L.jpg","A6_2024_7525_1-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1b90fd64-f68d-434b-b66d-3e927feeba25/original/as/A6_2024_7525_1-S.jpg","Q5_2024_6815_2_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2a88f953-4588-4f11-859e-deb07e3877da/original/as/Q5_2024_6815_2_withoutCast-L.jpg","A3_PA2_Sportback_HeaderAnimation_L.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:eb148e7f-505b-4dac-9205-3ac4526d1bbe/original/as/A3_PA2_Sportback_HeaderAnimation_L.mp4","A3_PA2_Sportback_SignatureCollection_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4a4a0782-5edd-4d3c-814d-a4c80d02b081/original/as/A3_PA2_Sportback_SignatureCollection_S.mp4","A3_PA2_Sportback_SeatingBallet_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:0d9ce15a-8bc3-4029-93c9-ae2bbe965cea/original/as/A3_PA2_Sportback_SeatingBallet_S.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/a3/a3-sportback</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:01:55.802Z</t>
+  </si>
+  <si>
+    <t>A3 Sportback Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/a3/a3-sportback/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-sportback-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>{"Q5_2024_7228_1_withoutCast-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:076ce57e-fa52-412d-a370-a268c3c37d42/original/as/Q5_2024_7228_1_withoutCast-S.jpg","Q5_2024_7231_1_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e68328f6-9a40-45e7-9f77-3826d3c2bdc2/original/as/Q5_2024_7231_1_withoutCast-L.jpg","Q5_2024_7227-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:70cf6eb0-37c1-46ee-9ad3-b1bcd4d107df/original/as/Q5_2024_7227-S-L.jpg","Q5_2024_7238_2_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ba45a2f5-eb34-4966-bc20-4e68a91f75e8/original/as/Q5_2024_7238_2_DE-S-L.jpg","Q5_2024_7236_3_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:c997fd62-e658-4127-97fb-286e108eb3b5/original/as/Q5_2024_7236_3_DE-S-L.jpg","Q5_2024_7233_1-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:470507cc-9091-4809-9c8d-e51dcdf77d66/original/as/Q5_2024_7233_1-S-L.jpg","Q5_2024_7230-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:293dc699-b0c4-4c42-abf4-dc318aeee7fc/original/as/Q5_2024_7230-S-L.jpg","Q5_2024_7221_1-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e5a2fa2d-ae83-41b8-b2a7-6e11f8d3f650/original/as/Q5_2024_7221_1-S-L.jpg","Q5_2024_7236_3_DE-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4f02d03c-d51a-4c8a-b395-4e4722a557ca/original/as/Q5_2024_7236_3_DE-L.jpg","Q5_2024_7235-800x600.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d2ff22b2-48b3-4b98-9e67-6dea5226739f/original/as/Q5_2024_7235-800x600.jpg","Q5_2024_7223_1_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:db328ea3-aafc-4484-acec-440bdba9ec00/original/as/Q5_2024_7223_1_withoutCast-L.jpg","Q5_2024_7228_1_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:14e22b7e-aeab-46d8-89d2-9bf4dd2e2c6a/original/as/Q5_2024_7228_1_withoutCast-L.jpg","ADM_as_2025_7857-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e0b7d047-a645-4cec-9d03-3e2d90f06e5c/original/as/ADM_as_2025_7857-L.jpg","Q3eh_SB_2025_8141-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:980af30d-40d0-4227-ae9e-8c5d17643c09/original/as/Q3eh_SB_2025_8141-L.jpg","A5_E_2024_7758_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:76d11bba-f807-467e-9d1c-6bcfa1944007/original/as/A5_E_2024_7758_1-L.jpg","A6eh_2024_7711_2-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ee53d506-7819-4426-9102-3ea639a1bee3/original/as/A6eh_2024_7711_2-L.jpg","20251103_Q5_SB_TFSIe_EU-Headeranimation.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:64acc011-4165-4fc5-bfc5-2766e79a0733/original/as/20251103_Q5_SB_TFSIe_EU-Headeranimation.mp4","20250605_Q5_TFSIe_Sportback_Light_Signature_1920x1920.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4626f39a-27d3-4a67-9c29-6718bca0bf87/original/as/20250605_Q5_TFSIe_Sportback_Light_Signature_1920x1920.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-sportback-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:02:22.607Z</t>
+  </si>
+  <si>
+    <t>Q5 Sportback e-hybrid Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/q5/q5-sportback-e-hybrid/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-sportback.report.json</t>
+  </si>
+  <si>
+    <t>{"Q5_2024_7162_2_withoutcast-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:f6d6f556-eda1-4088-a36b-94417d0caa3c/original/as/Q5_2024_7162_2_withoutcast-S.jpg","Q5_2024_7168_2-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:32cc0ba3-c955-4ef4-96d8-3c664058971c/original/as/Q5_2024_7168_2-L.jpg","Q5_2024_7163_V2-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:5abcedb3-0e67-4c09-bde1-c79ccb768eac/original/as/Q5_2024_7163_V2-L.jpg","Q5_2024_7176_2_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:f37c40c6-619d-4ae0-bc96-5b3dedf7cf72/original/as/Q5_2024_7176_2_DE-S-L.jpg","Q5_2024_7190_2_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:882da86e-425f-46d8-b034-fb9c22954c14/original/as/Q5_2024_7190_2_DE-S-L.jpg","Q5_2024_7168_2-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2377205a-d5ad-4993-a7d0-143f36f0a9df/original/as/Q5_2024_7168_2-S-L.jpg","Q5_2024_7192-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:50ae1705-8f31-43d6-83bd-2f644ebe46f9/original/as/Q5_2024_7192-S-L.jpg","Q5_2024_7162_2_withoutcast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:295f94f9-97f6-4851-b84f-3e5de96dd542/original/as/Q5_2024_7162_2_withoutcast-L.jpg","Q5_2024_7176_2_DE-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:b82281c7-1a94-4236-9cf1-2916e267bed6/original/as/Q5_2024_7176_2_DE-L.jpg","ADM_as_2025_7857-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e0b7d047-a645-4cec-9d03-3e2d90f06e5c/original/as/ADM_as_2025_7857-L.jpg","Q3_SB_2025_8112-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e2f18ce2-2d3d-4c5c-8937-c71a002dd0a7/original/as/Q3_SB_2025_8112-S-L.jpg","Q4_e_tron_PA_SB_AU316_Alpha_A_3_000_V6V6_Light-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2731c7f1-f7f8-451d-b3e7-d6be9c96c08c/original/as/Q4_e_tron_PA_SB_AU316_Alpha_A_3_000_V6V6_Light-L.png","Q8_2023_5476_1-L-2.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a8537579-2c45-42dc-b99a-95dc5f1b25fd/original/as/Q8_2023_5476_1-L-2.jpg","Q5_2024_7168_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:39700376-e363-4113-9a49-fc6d00009c94/original/as/Q5_2024_7168_1-L.jpg","20251103_Q5_SB_EU-Headeranimation.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2f9fbe4a-e1a4-4291-8b41-93f5be45fc26/original/as/20251103_Q5_SB_EU-Headeranimation.mp4","Q5_Sportback_Rearprojection_1920x1920.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:66180091-d4cd-448c-a93d-7a928b1cc579/original/as/Q5_Sportback_Rearprojection_1920x1920.mp4","Q5_Sportback_Light_Signature_1920x1920.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:9e2912d9-9f6d-4f9e-8d11-419c098eb00a/original/as/Q5_Sportback_Light_Signature_1920x1920.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-sportback</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:02:17.209Z</t>
+  </si>
+  <si>
+    <t>Q5 Sportback Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/q5/q5-sportback/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-suv-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>{"Q5_2024_6872_1_withoutCast-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:336eaa25-1dc5-45aa-a120-ca0cf239064f/original/as/Q5_2024_6872_1_withoutCast-S.jpg","Q5_2024_6865_1_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:56bd3aea-d100-4297-9f6f-090abde79538/original/as/Q5_2024_6865_1_withoutCast-L.jpg","Q5_2024_6869-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:80eaa1e1-075e-4dfc-a0c4-9e56f02bec1d/original/as/Q5_2024_6869-S-L.jpg","Q5_2024_6879_2_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:b8f94cd1-51e1-4f93-9297-b5d6db83bf81/original/as/Q5_2024_6879_2_DE-S-L.jpg","Q5_2024_6878_3_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:248172ad-4420-43d3-a74c-b3609c3525ca/original/as/Q5_2024_6878_3_DE-S-L.jpg","Q5_2024_6871_withoutCast-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:1a4bf21c-716c-4217-ab36-a4458a841d60/original/as/Q5_2024_6871_withoutCast-S-L.jpg","Q5_2024_6870-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8d1894a0-548d-4e21-b381-8b082d492723/original/as/Q5_2024_6870-S-L.jpg","Q5_2024_6872_1_withoutCast-L-new.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8d9b262b-2551-489f-b457-8719f6ec8b90/original/as/Q5_2024_6872_1_withoutCast-L-new.jpg","Q5_2024_6878_3_DE-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:f2967b72-d56a-4d44-9c32-b12ea87f9b98/original/as/Q5_2024_6878_3_DE-L.jpg","Q5_2024_6877-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:5996a326-c450-4c9e-98fe-a6e63674e746/original/as/Q5_2024_6877-S-L.jpg","Q5_2024_6873_1-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6dc5f92a-9be8-4c81-81ee-d5e0051853eb/original/as/Q5_2024_6873_1-S.jpg","ADM_as_2025_7857-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e0b7d047-a645-4cec-9d03-3e2d90f06e5c/original/as/ADM_as_2025_7857-L.jpg","Q3eh_2025_8094_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:53e295d2-ab23-40d0-9a83-bd8180e47e1b/original/as/Q3eh_2025_8094_1-L.jpg","A5_E_2024_7741_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:35270df1-d8f8-4e82-8465-97f09cfd117b/original/as/A5_E_2024_7741_1-L.jpg","A6eh_2024_7668_1-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:eeeb5cd4-30d4-49b6-af55-bcb1051fb04e/original/as/A6eh_2024_7668_1-L.jpg","Q5_2024_6872_1_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4434790f-19c5-4317-b720-441db12934bf/original/as/Q5_2024_6872_1_withoutCast-L.jpg","20251103_Q5_SUV_TFSIe_EU-Headeranimation.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d758bc60-889e-4e76-93fb-29aa301db8bd/original/as/20251103_Q5_SUV_TFSIe_EU-Headeranimation.mp4","20250605_Q5_TFSIe_SUV_NF_Light_Signature_1920x1920.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4b14104e-6140-449c-b89e-8a15e87ef44e/original/as/20250605_Q5_TFSIe_SUV_NF_Light_Signature_1920x1920.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-suv-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:02:10.662Z</t>
+  </si>
+  <si>
+    <t>Q5 SUV e-hybrid Highlights | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/q5/q5-suv-e-hybrid/</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-suv.report.json</t>
+  </si>
+  <si>
+    <t>{"Q5_2024_6823_V1_withoutCast-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4b9738b0-a87c-461c-a9f9-d71766ab24d9/original/as/Q5_2024_6823_V1_withoutCast-S.jpg","Q5_2024_6815_3_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cdd351f7-45b0-4a62-97cc-286c7e48c751/original/as/Q5_2024_6815_3_withoutCast-L.jpg","Q5_2024_6845_2-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:874409bb-c4c3-4d78-9757-9c93f3558c26/original/as/Q5_2024_6845_2-S-L.jpg","Q5_2024_6833_2_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d9c11e86-bcc5-4fd9-a424-8440fa607cfa/original/as/Q5_2024_6833_2_DE-S-L.jpg","Q5_2024_6835_3_DE-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:fd087027-f5f8-4dae-b827-f88afc85f8cd/original/as/Q5_2024_6835_3_DE-S-L.jpg","Q5_2024_6828-L-1.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:553f464b-2781-46c8-9dc1-a8f8735ffaf8/original/as/Q5_2024_6828-L-1.jpg","Q5_2024_6836_2-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:4bdbb540-36a2-4e0a-b1a9-fb8cd463d0ba/original/as/Q5_2024_6836_2-S-L.jpg","Q5_2024_6823_V1-S-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:59b7440d-1185-484b-8033-a11ee0f04b2d/original/as/Q5_2024_6823_V1-S-L.jpg","Q5_2024_6833_2_DE-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:11bdb6a1-72df-43ec-9478-47525efe0b07/original/as/Q5_2024_6833_2_DE-L.jpg","ADM_as_2025_7857-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e0b7d047-a645-4cec-9d03-3e2d90f06e5c/original/as/ADM_as_2025_7857-L.jpg","Q3_2025_8058_Cast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e15c6a3d-7dcb-4593-a630-92d44f138936/original/as/Q3_2025_8058_Cast-L.jpg","Q4_e_tron_PA_SUV_AU316_Alpha_A_3_000_3D3D_Light-L.png":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e7f9218f-f858-4bae-9f42-7fe4d0a90446/original/as/Q4_e_tron_PA_SUV_AU316_Alpha_A_3_000_3D3D_Light-L.png","Q8_2023_5476_1-L-2.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a8537579-2c45-42dc-b99a-95dc5f1b25fd/original/as/Q8_2023_5476_1-L-2.jpg","Q5_2024_6815_2_withoutCast-L.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:2a88f953-4588-4f11-859e-deb07e3877da/original/as/Q5_2024_6815_2_withoutCast-L.jpg","20251103_Q5_SUV_EU-Headeranimation.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:19929058-7069-404f-b9f9-62b9f5128bc1/original/as/20251103_Q5_SUV_EU-Headeranimation.mp4","Q5_SUV_NF_Rearprojection_1920x1920.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:beb31921-4801-4380-9cfb-3028e85c8f7f/original/as/Q5_SUV_NF_Rearprojection_1920x1920.mp4","Q5_SUV_SignatureCollection_S.mp4":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:0fd261f8-5480-430e-b240-cf6f0a32b895/original/as/Q5_SUV_SignatureCollection_S.mp4"}</t>
+  </si>
+  <si>
+    <t>de/neuwagen/q5/q5-suv</t>
+  </si>
+  <si>
+    <t>2026-10-26T22:02:05.836Z</t>
+  </si>
+  <si>
+    <t>Q5 SUV | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/q5/q5-suv/</t>
   </si>
 </sst>
 </file>
@@ -450,20 +624,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="43" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,38 +663,332 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-elektromobilitaet.report.xlsx
+++ b/tools/importer/reports/import-elektromobilitaet.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
   <si>
     <t>_reportFile</t>
   </si>
@@ -70,6 +70,15 @@
     <t>https://www.audi.de/de/elektromobilitaet/</t>
   </si>
   <si>
+    <t>language-masters/de/elektromobilitaet.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/elektromobilitaet</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:25.440Z</t>
+  </si>
+  <si>
     <t>de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
   </si>
   <si>
@@ -236,6 +245,87 @@
   </si>
   <si>
     <t>https://www.audi.de/de/neuwagen/q5/q5-suv/</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2-e-tron/a2-e-tron</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:18:04.106Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-allstreet.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-allstreet</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:17:49.306Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-limousine.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-limousine</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:17:45.380Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:17:53.107Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:17:58.005Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:18:21.706Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:18:17.588Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:18:13.506Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:18:09.161Z</t>
   </si>
 </sst>
 </file>
@@ -624,12 +714,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
@@ -704,287 +794,607 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="J6" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="I7" t="s">
         <v>46</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="J7" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="I8" t="s">
         <v>52</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="J8" t="s">
         <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="I9" t="s">
         <v>58</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="J9" t="s">
         <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="I10" t="s">
         <v>64</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="J10" t="s">
         <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="I11" t="s">
         <v>70</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="J11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>72</v>
       </c>
-      <c r="I11" t="s">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="J11" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
